--- a/data/Chiffres_fournisseurs.xlsx
+++ b/data/Chiffres_fournisseurs.xlsx
@@ -360,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.328125" customWidth="true"/>
@@ -398,7 +398,7 @@
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>As of 2026-05-04 09:00:09 Heure d'Europe centrale/CET • Generated by Damien Lauger</t>
+          <t>As of 2026-05-04 14:05:16 Heure d'Europe centrale/CET • Generated by Damien Lauger</t>
         </is>
       </c>
       <c r="C3" s="4"/>
@@ -531,75 +531,81 @@
     </row>
     <row r="14">
       <c r="A14" s="7"/>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Compteur segment equals c4</t>
-        </is>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="8"/>
     </row>
     <row r="15">
       <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Compteur segment  ↑</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Nom Fournisseur  ↑</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Average Prix Moyen Pondéré Non Margé</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Average Volume du compteur</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Record Count</t>
+        </is>
+      </c>
       <c r="G15" s="8"/>
     </row>
     <row r="16">
       <c r="A16" s="7"/>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Compteur segment  ↑</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Nom Fournisseur  ↑</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Average Prix Moyen Pondéré Non Margé</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Average Volume du compteur</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Record Count</t>
-        </is>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>ALTERNA ENERGIE</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>61.663333333333334</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>42085.08666666667</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>3.0</v>
       </c>
       <c r="G16" s="8"/>
     </row>
     <row r="17">
       <c r="A17" s="7"/>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
+      <c r="B17" s="15"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>ALTERNA ENERGIE</t>
+          <t>ENERGEM</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>74.39382352941176</v>
+        <v>61.97</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>151.20382352941178</v>
+        <v>57964.63</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>34.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="8"/>
     </row>
@@ -608,14 +614,14 @@
       <c r="B18" s="15"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>BCM ENERGY</t>
+          <t>HELLIO SOLUTIONS</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>71.73</v>
+        <v>60.275</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>155.405</v>
+        <v>34145.315</v>
       </c>
       <c r="F18" s="14" t="n">
         <v>2.0</v>
@@ -627,17 +633,17 @@
       <c r="B19" s="15"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>DYNEFF S A S</t>
+          <t>LA BELLENERGIE</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>65.03070422535211</v>
+        <v>57.815</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>118.80943661971831</v>
+        <v>57964.63</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>71.0</v>
+        <v>2.0</v>
       </c>
       <c r="G19" s="8"/>
     </row>
@@ -646,17 +652,17 @@
       <c r="B20" s="15"/>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>EKWATEUR PRO</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>70.86627450980392</v>
+        <v>67.19</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>83.87382352941177</v>
+        <v>10326.0</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>102.0</v>
+        <v>1.0</v>
       </c>
       <c r="G20" s="8"/>
     </row>
@@ -665,17 +671,17 @@
       <c r="B21" s="15"/>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>ENDESA ENERGIA SUCCURSAL FRANCE</t>
+          <t>OHM ENERGIE</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>63.06267857142857</v>
+        <v>58.15</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>104.38982142857142</v>
+        <v>42085.08666666667</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>56.0</v>
+        <v>3.0</v>
       </c>
       <c r="G21" s="8"/>
     </row>
@@ -684,17 +690,17 @@
       <c r="B22" s="15"/>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>ENERGEM</t>
+          <t>PRIMEO ENERGIE FRANCE</t>
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>66.22066666666667</v>
+        <v>60.905</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>90.96228571428571</v>
+        <v>46054.9725</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>210.0</v>
+        <v>4.0</v>
       </c>
       <c r="G22" s="8"/>
     </row>
@@ -703,55 +709,59 @@
       <c r="B23" s="15"/>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>ENGIE</t>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>69.61206896551724</v>
+        <v>61.13</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>76.2544827586207</v>
+        <v>42085.08666666667</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>29.0</v>
+        <v>3.0</v>
       </c>
       <c r="G23" s="8"/>
     </row>
     <row r="24">
       <c r="A24" s="7"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Enovos Luxembourg S.A.</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>66.60642857142857</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>185.04785714285714</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>14.0</v>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18" t="n">
+        <v>60.620526315789476</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>42920.852105263155</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>19.0</v>
       </c>
       <c r="G24" s="8"/>
     </row>
     <row r="25">
       <c r="A25" s="7"/>
-      <c r="B25" s="15"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>GEDIA ENERGIES &amp; SERVICES</t>
+          <t>ALTERNA ENERGIE</t>
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>64.7684</v>
+        <v>64.1</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>151.7932</v>
+        <v>3122.33</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="G25" s="8"/>
     </row>
@@ -760,17 +770,17 @@
       <c r="B26" s="15"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>GEG SOURCE D'ENERGIES</t>
+          <t>BCM ENERGY</t>
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>73.81857142857143</v>
+        <v>62.0</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>102.30380952380952</v>
+        <v>162.66</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>21.0</v>
+        <v>2.0</v>
       </c>
       <c r="G26" s="8"/>
     </row>
@@ -779,17 +789,17 @@
       <c r="B27" s="15"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>HELLIO SOLUTIONS</t>
+          <t>DYNEFF S A S</t>
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>68.09931972789116</v>
+        <v>68.75533333333334</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>93.72809523809524</v>
+        <v>675.778</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>147.0</v>
+        <v>15.0</v>
       </c>
       <c r="G27" s="8"/>
     </row>
@@ -798,17 +808,17 @@
       <c r="B28" s="15"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>LA BELLENERGIE</t>
+          <t>EKWATEUR PRO</t>
         </is>
       </c>
       <c r="D28" s="13" t="n">
-        <v>64.63854166666667</v>
+        <v>76.57</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>119.75375</v>
+        <v>107.53</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>48.0</v>
+        <v>3.0</v>
       </c>
       <c r="G28" s="8"/>
     </row>
@@ -817,17 +827,17 @@
       <c r="B29" s="15"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>ENDESA ENERGIA SUCCURSAL FRANCE</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>70.29642857142858</v>
+        <v>63.52076923076923</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>94.67517857142857</v>
+        <v>1337.3284615384616</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>168.0</v>
+        <v>13.0</v>
       </c>
       <c r="G29" s="8"/>
     </row>
@@ -836,17 +846,17 @@
       <c r="B30" s="15"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>OHM ENERGIE</t>
+          <t>ENERGEM</t>
         </is>
       </c>
       <c r="D30" s="13" t="n">
-        <v>63.104285714285716</v>
+        <v>66.42432989690721</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>206.79714285714286</v>
+        <v>338.33762886597935</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>7.0</v>
+        <v>97.0</v>
       </c>
       <c r="G30" s="8"/>
     </row>
@@ -855,17 +865,17 @@
       <c r="B31" s="15"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>PRIMEO ENERGIE FRANCE</t>
+          <t>ENGIE</t>
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>67.328</v>
+        <v>65.99666666666667</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>101.94766666666666</v>
+        <v>664.0566666666666</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>90.0</v>
+        <v>9.0</v>
       </c>
       <c r="G31" s="8"/>
     </row>
@@ -874,17 +884,17 @@
       <c r="B32" s="15"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+          <t>Enovos Luxembourg S.A.</t>
         </is>
       </c>
       <c r="D32" s="13" t="n">
-        <v>66.86166666666666</v>
+        <v>63.476</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>88.3586231884058</v>
+        <v>326.254</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>138.0</v>
+        <v>5.0</v>
       </c>
       <c r="G32" s="8"/>
     </row>
@@ -893,17 +903,17 @@
       <c r="B33" s="15"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SYNELVA</t>
+          <t>GEDIA ENERGIES &amp; SERVICES</t>
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>64.77</v>
+        <v>62.554</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>51.28181818181818</v>
+        <v>1305.138</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="G33" s="8"/>
     </row>
@@ -912,17 +922,17 @@
       <c r="B34" s="15"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>TOTALENERGIES ELECTRICITE ET GAZ FRANCE</t>
+          <t>GEG SOURCE D'ENERGIES</t>
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>86.95571428571428</v>
+        <v>72.59</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>105.08428571428571</v>
+        <v>253.875</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" s="8"/>
     </row>
@@ -931,57 +941,1943 @@
       <c r="B35" s="15"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>UNION DES PRODUCTEURS LOCAUX D'ELECTRICITE</t>
+          <t>HELLIO SOLUTIONS</t>
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>71.80247863247864</v>
+        <v>70.95357142857142</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>81.29350427350427</v>
+        <v>950.4257142857143</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>117.0</v>
+        <v>14.0</v>
       </c>
       <c r="G35" s="8"/>
     </row>
     <row r="36">
       <c r="A36" s="7"/>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18" t="n">
-        <v>68.16713302752294</v>
-      </c>
-      <c r="E36" s="19" t="n">
-        <v>97.67480122324159</v>
-      </c>
-      <c r="F36" s="19" t="n">
-        <v>1308.0</v>
+      <c r="B36" s="15"/>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>LA BELLENERGIE</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>70.384</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>898.5935</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>20.0</v>
       </c>
       <c r="G36" s="8"/>
     </row>
     <row r="37">
       <c r="A37" s="7"/>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="15"/>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>MINT</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>73.9074074074074</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>1066.0762962962963</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="G37" s="8"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>OHM ENERGIE</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>64.82666666666667</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>1139.6683333333333</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G38" s="8"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>PRIMEO ENERGIE FRANCE</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>67.13765306122448</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>394.69867346938776</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>98.0</v>
+      </c>
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>67.59</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>1263.751052631579</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="G40" s="8"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>SYNELVA</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>181.74305555555554</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="G41" s="8"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>UNION DES PRODUCTEURS LOCAUX D'ELECTRICITE</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>73.012</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>732.1</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G42" s="8"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>VATTENFALL ENERGIES</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>59.755</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>3084.06</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G43" s="8"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7"/>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="18" t="n">
+        <v>67.37293193717278</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>612.5801308900524</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>382.0</v>
+      </c>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>ALTERNA ENERGIE</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>74.39382352941176</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>151.20382352941178</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="G45" s="8"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>BCM ENERGY</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>71.73</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>155.405</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G46" s="8"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>DYNEFF S A S</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>65.03070422535211</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>118.80943661971831</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="G47" s="8"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>EKWATEUR PRO</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>70.86627450980392</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>83.87382352941177</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>102.0</v>
+      </c>
+      <c r="G48" s="8"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>ENDESA ENERGIA SUCCURSAL FRANCE</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>63.16555555555556</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>108.05203703703704</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="G49" s="8"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>ENERGEM</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>66.21198113207546</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>91.06084905660377</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>212.0</v>
+      </c>
+      <c r="G50" s="8"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>ENGIE</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>69.61206896551724</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>76.2544827586207</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="G51" s="8"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Enovos Luxembourg S.A.</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="n">
+        <v>66.60642857142857</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>185.04785714285714</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G52" s="8"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>GEDIA ENERGIES &amp; SERVICES</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>65.0773076923077</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>149.9726923076923</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="G53" s="8"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>GEG SOURCE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>73.81857142857143</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>102.30380952380952</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="G54" s="8"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>HELLIO SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>68.07333333333334</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>93.72809523809524</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>147.0</v>
+      </c>
+      <c r="G55" s="8"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>LA BELLENERGIE</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>64.63854166666667</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>119.75375</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="G56" s="8"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>MINT</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="n">
+        <v>70.3649090909091</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>94.30884848484848</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>165.0</v>
+      </c>
+      <c r="G57" s="8"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>OHM ENERGIE</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>63.104285714285716</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>206.79714285714286</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="G58" s="8"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>PRIMEO ENERGIE FRANCE</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>67.328</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>101.94766666666666</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="G59" s="8"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>66.85214814814815</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>87.77051851851851</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>135.0</v>
+      </c>
+      <c r="G60" s="8"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>SYNELVA</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>51.28181818181818</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="G61" s="8"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>TOTALENERGIES ELECTRICITE ET GAZ FRANCE</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>89.562</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>144.914</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G62" s="8"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>UNION DES PRODUCTEURS LOCAUX D'ELECTRICITE</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>71.80247863247864</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>81.29350427350427</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="G63" s="8"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7"/>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C64" s="17"/>
+      <c r="D64" s="18" t="n">
+        <v>68.16239815526518</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>97.8900384319754</v>
+      </c>
+      <c r="F64" s="19" t="n">
+        <v>1301.0</v>
+      </c>
+      <c r="G64" s="8"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7"/>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>ALTERNA ENERGIE</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>90.15666666666667</v>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>29.073333333333334</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G65" s="8"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>BCM ENERGY</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>73.18</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>60.07</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G66" s="8"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>DYNEFF S A S</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>69.52484210526316</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>14.984736842105264</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="G67" s="8"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>EKWATEUR PRO</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="n">
+        <v>70.42355504587157</v>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>11.912419724770642</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>872.0</v>
+      </c>
+      <c r="G68" s="8"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>ENDESA ENERGIA SUCCURSAL FRANCE</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="n">
+        <v>73.34965116279069</v>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>16.41906976744186</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="G69" s="8"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>ENERGEM</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="n">
+        <v>66.59581395348837</v>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>19.338488372093025</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="G70" s="8"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>ENGIE</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>73.47769230769231</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>21.99692307692308</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="G71" s="8"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>GEDIA ENERGIES &amp; SERVICES</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="n">
+        <v>71.945</v>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v>6.735</v>
+      </c>
+      <c r="F72" s="14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G72" s="8"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>GEG SOURCE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="n">
+        <v>73.78370370370371</v>
+      </c>
+      <c r="E73" s="14" t="n">
+        <v>30.616666666666667</v>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="G73" s="8"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>HELLIO SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="n">
+        <v>76.93545454545455</v>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v>23.005454545454544</v>
+      </c>
+      <c r="F74" s="14" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="G74" s="8"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>ILEK</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="n">
+        <v>134.0925</v>
+      </c>
+      <c r="E75" s="14" t="n">
+        <v>10.153333333333334</v>
+      </c>
+      <c r="F75" s="14" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="G75" s="8"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>LA BELLENERGIE</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="n">
+        <v>69.697304964539</v>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>12.936312056737588</v>
+      </c>
+      <c r="F76" s="14" t="n">
+        <v>141.0</v>
+      </c>
+      <c r="G76" s="8"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>MINT</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="n">
+        <v>75.04994029850747</v>
+      </c>
+      <c r="E77" s="14" t="n">
+        <v>11.801303482587064</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>1005.0</v>
+      </c>
+      <c r="G77" s="8"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>OHM ENERGIE</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="n">
+        <v>74.65666666666667</v>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G78" s="8"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>PRIMEO ENERGIE FRANCE</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="n">
+        <v>67.06140845070422</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>17.22619718309859</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="G79" s="8"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="n">
+        <v>70.2695</v>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G80" s="8"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>SYNELVA</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>18.234516129032258</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="G81" s="8"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>TOTALENERGIES ELECTRICITE ET GAZ FRANCE</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>92.17575757575757</v>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>12.027424242424242</v>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="G82" s="8"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>UNION DES PRODUCTEURS LOCAUX D'ELECTRICITE</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="n">
+        <v>67.42406022845275</v>
+      </c>
+      <c r="E83" s="14" t="n">
+        <v>11.24453790238837</v>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>963.0</v>
+      </c>
+      <c r="G83" s="8"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>VATTENFALL ENERGIES</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="n">
+        <v>83.69507936507937</v>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v>12.546031746031746</v>
+      </c>
+      <c r="F84" s="14" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="G84" s="8"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7"/>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C85" s="17"/>
+      <c r="D85" s="18" t="n">
+        <v>71.96934649610678</v>
+      </c>
+      <c r="E85" s="19" t="n">
+        <v>12.625494994438265</v>
+      </c>
+      <c r="F85" s="19" t="n">
+        <v>3596.0</v>
+      </c>
+      <c r="G85" s="8"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7"/>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>DYNEFF S A S</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="n">
+        <v>31.6775</v>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v>10.4028125</v>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="G86" s="8"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>EKWATEUR PRO</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="E87" s="14" t="n">
+        <v>7.493333333333333</v>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G87" s="8"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>ENDESA ENERGIA SUCCURSAL FRANCE</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>11.3965</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G88" s="8"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>GAZ DE BORDEAUX</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="n">
+        <v>29.4836</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>7.4576</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="G89" s="8"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>GEDIA ENERGIES &amp; SERVICES</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G90" s="8"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>OHM ENERGIE</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>7.493333333333333</v>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G91" s="8"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>PICOTY</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G92" s="8"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>SEFE ENERGY SAS</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>7.493333333333333</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G93" s="8"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>7.493333333333333</v>
+      </c>
+      <c r="F94" s="14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G94" s="8"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7"/>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C95" s="17"/>
+      <c r="D95" s="18" t="n">
+        <v>33.06344537815126</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>8.518319327731092</v>
+      </c>
+      <c r="F95" s="19" t="n">
+        <v>119.0</v>
+      </c>
+      <c r="G95" s="8"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7"/>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>ALTERNA ENERGIE</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G96" s="8"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>DYNEFF S A S</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="n">
+        <v>31.899910714285713</v>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>70.25330357142857</v>
+      </c>
+      <c r="F97" s="14" t="n">
+        <v>112.0</v>
+      </c>
+      <c r="G97" s="8"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>EKWATEUR PRO</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>35.989</v>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>54.90211111111111</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="G98" s="8"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>ENDESA ENERGIA SUCCURSAL FRANCE</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="n">
+        <v>37.53688888888889</v>
+      </c>
+      <c r="E99" s="14" t="n">
+        <v>79.42911111111111</v>
+      </c>
+      <c r="F99" s="14" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="G99" s="8"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7"/>
+      <c r="B100" s="15"/>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>ENERGEM</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="n">
+        <v>32.9775</v>
+      </c>
+      <c r="E100" s="14" t="n">
+        <v>109.96125</v>
+      </c>
+      <c r="F100" s="14" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="G100" s="8"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7"/>
+      <c r="B101" s="15"/>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>ENGIE</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>39.172</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>106.446</v>
+      </c>
+      <c r="F101" s="14" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G101" s="8"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7"/>
+      <c r="B102" s="15"/>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Enovos Luxembourg S.A.</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="F102" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G102" s="8"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7"/>
+      <c r="B103" s="15"/>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>GAZ DE BORDEAUX</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>34.52781512605042</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>63.28806722689075</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>119.0</v>
+      </c>
+      <c r="G103" s="8"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7"/>
+      <c r="B104" s="15"/>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>GAZ DE PARIS</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="n">
+        <v>33.948</v>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v>123.792</v>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G104" s="8"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7"/>
+      <c r="B105" s="15"/>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>GEDIA ENERGIES &amp; SERVICES</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="n">
+        <v>34.50833333333333</v>
+      </c>
+      <c r="E105" s="14" t="n">
+        <v>106.005</v>
+      </c>
+      <c r="F105" s="14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G105" s="8"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>ILEK</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F106" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G106" s="8"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7"/>
+      <c r="B107" s="15"/>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>NATGAS FRANCE</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="E107" s="14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F107" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G107" s="8"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7"/>
+      <c r="B108" s="15"/>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>OHM ENERGIE</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="n">
+        <v>31.36267441860465</v>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v>53.979418604651165</v>
+      </c>
+      <c r="F108" s="14" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="G108" s="8"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7"/>
+      <c r="B109" s="15"/>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>PICOTY</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="n">
+        <v>39.22541666666667</v>
+      </c>
+      <c r="E109" s="14" t="n">
+        <v>24.085833333333333</v>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="G109" s="8"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>SEFE ENERGY SAS</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="n">
+        <v>32.212</v>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v>54.547304347826085</v>
+      </c>
+      <c r="F110" s="14" t="n">
+        <v>115.0</v>
+      </c>
+      <c r="G110" s="8"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7"/>
+      <c r="B111" s="15"/>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>30.432441860465115</v>
+      </c>
+      <c r="E111" s="14" t="n">
+        <v>53.979418604651165</v>
+      </c>
+      <c r="F111" s="14" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="G111" s="8"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7"/>
+      <c r="B112" s="15"/>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>TOTALENERGIES ELECTRICITE ET GAZ FRANCE</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="n">
+        <v>59.558571428571426</v>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v>31.08142857142857</v>
+      </c>
+      <c r="F112" s="14" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G112" s="8"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7"/>
+      <c r="B113" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C113" s="17"/>
+      <c r="D113" s="18" t="n">
+        <v>34.05529005524862</v>
+      </c>
+      <c r="E113" s="19" t="n">
+        <v>60.51816298342541</v>
+      </c>
+      <c r="F113" s="19" t="n">
+        <v>724.0</v>
+      </c>
+      <c r="G113" s="8"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7"/>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>ALTERNA ENERGIE</t>
+        </is>
+      </c>
+      <c r="D114" s="13" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v>4147.08</v>
+      </c>
+      <c r="F114" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G114" s="8"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7"/>
+      <c r="B115" s="15"/>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>DYNEFF S A S</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>31.9004</v>
+      </c>
+      <c r="E115" s="14" t="n">
+        <v>931.9202666666666</v>
+      </c>
+      <c r="F115" s="14" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="G115" s="8"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7"/>
+      <c r="B116" s="15"/>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>EKWATEUR PRO</t>
+        </is>
+      </c>
+      <c r="D116" s="13" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v>870.7703703703704</v>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="G116" s="8"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7"/>
+      <c r="B117" s="15"/>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>ENDESA ENERGIA SUCCURSAL FRANCE</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="n">
+        <v>35.491875</v>
+      </c>
+      <c r="E117" s="14" t="n">
+        <v>462.32875</v>
+      </c>
+      <c r="F117" s="14" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="G117" s="8"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>ENERGEM</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="n">
+        <v>29.243333333333332</v>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v>1581.6166666666666</v>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G118" s="8"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>ENGIE</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="n">
+        <v>32.20666666666666</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>376.3466666666667</v>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G119" s="8"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7"/>
+      <c r="B120" s="15"/>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Enovos Luxembourg S.A.</t>
+        </is>
+      </c>
+      <c r="D120" s="13" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v>2674.64</v>
+      </c>
+      <c r="F120" s="14" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G120" s="8"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7"/>
+      <c r="B121" s="15"/>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>GAZ DE BORDEAUX</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="n">
+        <v>33.237272727272725</v>
+      </c>
+      <c r="E121" s="14" t="n">
+        <v>911.6519696969697</v>
+      </c>
+      <c r="F121" s="14" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="G121" s="8"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7"/>
+      <c r="B122" s="15"/>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>GAZ DE PARIS</t>
+        </is>
+      </c>
+      <c r="D122" s="13" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v>181.315</v>
+      </c>
+      <c r="F122" s="14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G122" s="8"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7"/>
+      <c r="B123" s="15"/>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>GEDIA ENERGIES &amp; SERVICES</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="n">
+        <v>33.91111111111111</v>
+      </c>
+      <c r="E123" s="14" t="n">
+        <v>1008.7688888888889</v>
+      </c>
+      <c r="F123" s="14" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G123" s="8"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7"/>
+      <c r="B124" s="15"/>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>NATGAS FRANCE</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="n">
+        <v>29.742</v>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v>1668.6</v>
+      </c>
+      <c r="F124" s="14" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G124" s="8"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7"/>
+      <c r="B125" s="15"/>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>OHM ENERGIE</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="n">
+        <v>31.07372881355932</v>
+      </c>
+      <c r="E125" s="14" t="n">
+        <v>934.8033898305084</v>
+      </c>
+      <c r="F125" s="14" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="G125" s="8"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="7"/>
+      <c r="B126" s="15"/>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>PICOTY</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v>473.22</v>
+      </c>
+      <c r="F126" s="14" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G126" s="8"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="7"/>
+      <c r="B127" s="15"/>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>SEFE ENERGY SAS</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="n">
+        <v>31.3765625</v>
+      </c>
+      <c r="E127" s="14" t="n">
+        <v>936.345</v>
+      </c>
+      <c r="F127" s="14" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="G127" s="8"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="7"/>
+      <c r="B128" s="15"/>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="n">
+        <v>30.21890625</v>
+      </c>
+      <c r="E128" s="14" t="n">
+        <v>1023.308125</v>
+      </c>
+      <c r="F128" s="14" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="G128" s="8"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="7"/>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C129" s="17"/>
+      <c r="D129" s="18" t="n">
+        <v>32.260892448512585</v>
+      </c>
+      <c r="E129" s="19" t="n">
+        <v>940.1739359267734</v>
+      </c>
+      <c r="F129" s="19" t="n">
+        <v>437.0</v>
+      </c>
+      <c r="G129" s="8"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="7"/>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>ALTERNA ENERGIE</t>
+        </is>
+      </c>
+      <c r="D130" s="13" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="E130" s="14" t="n">
+        <v>52497.97</v>
+      </c>
+      <c r="F130" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G130" s="8"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7"/>
+      <c r="B131" s="15"/>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>OHM ENERGIE</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E131" s="14" t="n">
+        <v>52497.97</v>
+      </c>
+      <c r="F131" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G131" s="8"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="7"/>
+      <c r="B132" s="15"/>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>SEFE ENERGY SAS</t>
+        </is>
+      </c>
+      <c r="D132" s="13" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="E132" s="14" t="n">
+        <v>52497.97</v>
+      </c>
+      <c r="F132" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G132" s="8"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="7"/>
+      <c r="B133" s="15"/>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>SOCIETE D'APPROVISIONNEMENT ET DE VENTE D'ENERGIES</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="E133" s="14" t="n">
+        <v>52497.97</v>
+      </c>
+      <c r="F133" s="14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G133" s="8"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7"/>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="C134" s="17"/>
+      <c r="D134" s="18" t="n">
+        <v>26.715</v>
+      </c>
+      <c r="E134" s="19" t="n">
+        <v>52497.97</v>
+      </c>
+      <c r="F134" s="19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G134" s="8"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="7"/>
+      <c r="B135" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="22" t="n">
-        <v>68.16713302752294</v>
-      </c>
-      <c r="E37" s="23" t="n">
-        <v>97.67480122324159</v>
-      </c>
-      <c r="F37" s="23" t="n">
-        <v>1308.0</v>
-      </c>
-      <c r="G37" s="8"/>
+      <c r="C135" s="21"/>
+      <c r="D135" s="22" t="n">
+        <v>63.37963384989365</v>
+      </c>
+      <c r="E135" s="23" t="n">
+        <v>286.8329899726527</v>
+      </c>
+      <c r="F135" s="23" t="n">
+        <v>6582.0</v>
+      </c>
+      <c r="G135" s="8"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
